--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.11732835840925</v>
+        <v>10.4190658582415</v>
       </c>
       <c r="D2" t="n">
-        <v>9.882808647572352</v>
+        <v>1.605956405230507</v>
       </c>
       <c r="E2" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F2" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.57048313539459</v>
+        <v>3.017703509501621</v>
       </c>
       <c r="D3" t="n">
-        <v>18.25116487761292</v>
+        <v>2.965814292612099</v>
       </c>
       <c r="E3" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F3" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.28285895342571</v>
+        <v>8.495964579931679</v>
       </c>
       <c r="D4" t="n">
-        <v>6.952240723404862</v>
+        <v>1.12973911755329</v>
       </c>
       <c r="E4" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F4" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.49994925747298</v>
+        <v>11.13124175433936</v>
       </c>
       <c r="D5" t="n">
-        <v>43.43809229403036</v>
+        <v>7.058689997779934</v>
       </c>
       <c r="E5" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F5" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>68.45536016901123</v>
+        <v>11.12399602746433</v>
       </c>
       <c r="D6" t="n">
-        <v>35.0256835189556</v>
+        <v>5.691673571830286</v>
       </c>
       <c r="E6" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F6" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>78.26162977860147</v>
+        <v>12.71751483902274</v>
       </c>
       <c r="D7" t="n">
-        <v>57.55308283365595</v>
+        <v>9.352375960469091</v>
       </c>
       <c r="E7" t="n">
-        <v>19.38252535200675</v>
+        <v>3.149660369701097</v>
       </c>
       <c r="F7" t="n">
-        <v>18.37459914893563</v>
+        <v>2.985872361702041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
